--- a/PPREstimation/output/top10/32_1_Arabian_Sea_off_Karnataka_(2000).xlsx
+++ b/PPREstimation/output/top10/32_1_Arabian_Sea_off_Karnataka_(2000).xlsx
@@ -617,7 +617,6 @@
           <t>Import</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
@@ -640,10 +639,10 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>0</v>
@@ -2805,7 +2804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2943,6 +2942,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -2953,9 +2962,6 @@
           <t>diet_import</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
@@ -2986,19 +2992,19 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3011,9 +3017,6 @@
           <t>Detritus</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
@@ -3063,6 +3066,9 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3075,9 +3081,6 @@
           <t>Phytoplankton</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
@@ -3127,6 +3130,9 @@
         <v>1</v>
       </c>
       <c r="V4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3139,11 +3145,8 @@
           <t>Micro Zooplankton</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
-        <v>4.881896884283592</v>
+        <v>6.223128848904347</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>5.102040816326531</v>
@@ -3192,6 +3195,9 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>5.124599030923125</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.881896884283592</v>
       </c>
     </row>
     <row r="6">
@@ -3203,11 +3209,8 @@
           <t>Large zooplankton</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n">
-        <v>15.94929274210823</v>
+        <v>25.20558388046248</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>22.27429047420717</v>
@@ -3256,6 +3259,9 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>22.32385000367074</v>
+      </c>
+      <c r="X6" t="n">
+        <v>15.94929274210823</v>
       </c>
     </row>
     <row r="7">
@@ -3267,11 +3273,8 @@
           <t>Micro Nekton</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>52.8465198923722</v>
+        <v>103.5813817095471</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>117.3357669362273</v>
@@ -3320,6 +3323,9 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>135.1944639731009</v>
+      </c>
+      <c r="X7" t="n">
+        <v>52.8465198923722</v>
       </c>
     </row>
     <row r="8">
@@ -3331,11 +3337,8 @@
           <t>Meiobenthos</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="n">
-        <v>0.05254773126183929</v>
+        <v>0.08367779418903544</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0.09612080757235872</v>
@@ -3384,6 +3387,9 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>0.119552806205362</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.05254773126183929</v>
       </c>
     </row>
     <row r="9">
@@ -3395,11 +3401,8 @@
           <t>Heterotrophic Benthos</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
-        <v>6.891211836915105</v>
+        <v>13.13335276301223</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>62.62495666609252</v>
@@ -3448,6 +3451,9 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>210.6771933229766</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6.891211836915105</v>
       </c>
     </row>
     <row r="10">
@@ -3459,11 +3465,8 @@
           <t>Benthic Omnivores</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n">
-        <v>10.30716214090233</v>
+        <v>23.42316035580676</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>58.86643558878648</v>
@@ -3512,6 +3515,9 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>191.0637789111209</v>
+      </c>
+      <c r="X10" t="n">
+        <v>10.30716214090233</v>
       </c>
     </row>
     <row r="11">
@@ -3523,11 +3529,8 @@
           <t>Shrimps</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n">
-        <v>43.82355419599745</v>
+        <v>90.21080501805984</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>40.50231375945157</v>
@@ -3576,6 +3579,9 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>47.24459970241958</v>
+      </c>
+      <c r="X11" t="n">
+        <v>43.82355419599745</v>
       </c>
     </row>
     <row r="12">
@@ -3587,11 +3593,8 @@
           <t>Crabs &amp; Lobster</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="n">
-        <v>20.91214152184571</v>
+        <v>56.11716397410842</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>45.04131904158248</v>
@@ -3640,6 +3643,9 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>98.84681219182602</v>
+      </c>
+      <c r="X12" t="n">
+        <v>20.91214152184571</v>
       </c>
     </row>
     <row r="13">
@@ -3651,11 +3657,8 @@
           <t>Anchovies</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="n">
-        <v>85.29867757995484</v>
+        <v>185.3606009254594</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>283.8477380659185</v>
@@ -3704,6 +3707,9 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>323.6420722797649</v>
+      </c>
+      <c r="X13" t="n">
+        <v>85.29867757995484</v>
       </c>
     </row>
     <row r="14">
@@ -3715,11 +3721,8 @@
           <t>Clupeids</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="n">
-        <v>62.51718857610121</v>
+        <v>139.0360670903112</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>124.0840822817122</v>
@@ -3768,6 +3771,9 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>137.3658946426152</v>
+      </c>
+      <c r="X14" t="n">
+        <v>62.51718857610121</v>
       </c>
     </row>
     <row r="15">
@@ -3779,11 +3785,8 @@
           <t>Mackerel</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="n">
-        <v>4.359533917665248</v>
+        <v>5.557254062071582</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>9.106403715332288</v>
@@ -3832,6 +3835,9 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>9.142999596962323</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4.359533917665248</v>
       </c>
     </row>
     <row r="16">
@@ -3843,11 +3849,8 @@
           <t>Small Benthopelagics</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>254.9523014578453</v>
+        <v>728.5926525649658</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>919.9061492990342</v>
@@ -3896,6 +3899,9 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>1401.621854227955</v>
+      </c>
+      <c r="X16" t="n">
+        <v>254.9523014578453</v>
       </c>
     </row>
     <row r="17">
@@ -3907,11 +3913,8 @@
           <t>Small Benthic Carnivores</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="n">
-        <v>41.09131584504831</v>
+        <v>95.79166706484966</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>100.5572347261105</v>
@@ -3960,6 +3963,9 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>151.2584807094888</v>
+      </c>
+      <c r="X17" t="n">
+        <v>41.09131584504831</v>
       </c>
     </row>
     <row r="18">
@@ -3971,11 +3977,8 @@
           <t>Med Benthic Carnivores</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" s="2" t="n">
-        <v>94.4422691586573</v>
+        <v>225.140772807137</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>142.3376778995271</v>
@@ -4024,6 +4027,9 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>193.4812320887115</v>
+      </c>
+      <c r="X18" t="n">
+        <v>94.4422691586573</v>
       </c>
     </row>
     <row r="19">
@@ -4035,11 +4041,8 @@
           <t>Large Benthic Carnivores</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" s="2" t="n">
-        <v>220.4948512678794</v>
+        <v>610.0910780918889</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>361.1000248236857</v>
@@ -4088,6 +4091,9 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>1087.7355054648</v>
+      </c>
+      <c r="X19" t="n">
+        <v>220.4948512678794</v>
       </c>
     </row>
     <row r="20">
@@ -4099,11 +4105,8 @@
           <t>Large Benthopelagics</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" s="2" t="n">
-        <v>473.906881375648</v>
+        <v>1636.44010918869</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>891.279786561407</v>
@@ -4152,6 +4155,9 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>1862.209046119513</v>
+      </c>
+      <c r="X20" t="n">
+        <v>473.906881375648</v>
       </c>
     </row>
     <row r="21">
@@ -4163,11 +4169,8 @@
           <t>Cephalopods</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" s="2" t="n">
-        <v>347.7981575665012</v>
+        <v>1064.398658569565</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1184.851684023025</v>
@@ -4216,6 +4219,9 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>2896.825960442839</v>
+      </c>
+      <c r="X21" t="n">
+        <v>347.7981575665012</v>
       </c>
     </row>
     <row r="22">
@@ -4227,11 +4233,8 @@
           <t>Tunas</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="n">
-        <v>333.0254672490636</v>
+        <v>972.6576464312997</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>751.7539715348304</v>
@@ -4280,6 +4283,9 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>949.2664681204172</v>
+      </c>
+      <c r="X22" t="n">
+        <v>333.0254672490636</v>
       </c>
     </row>
     <row r="23">
@@ -4291,11 +4297,8 @@
           <t>Large Pelagics</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="n">
-        <v>581.4580268409309</v>
+        <v>2235.112916068463</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>734.6257685687615</v>
@@ -4344,6 +4347,9 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>1940.538493448634</v>
+      </c>
+      <c r="X23" t="n">
+        <v>581.4580268409309</v>
       </c>
     </row>
     <row r="24">
@@ -4355,11 +4361,8 @@
           <t>Skates &amp; Rays</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="n">
-        <v>204.450412950168</v>
+        <v>622.2719892432722</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>1723.249235490315</v>
@@ -4408,6 +4411,9 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>2884.025385365229</v>
+      </c>
+      <c r="X24" t="n">
+        <v>204.450412950168</v>
       </c>
     </row>
     <row r="25">
@@ -4419,11 +4425,8 @@
           <t>Sharks</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="n">
-        <v>1164.579641210795</v>
+        <v>5105.589709036698</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>1695.298486256927</v>
@@ -4473,6 +4476,9 @@
       <c r="V25" s="2" t="n">
         <v>3847.70452912626</v>
       </c>
+      <c r="X25" t="n">
+        <v>1164.579641210795</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -4483,11 +4489,8 @@
           <t>Marine Mammals</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="n">
-        <v>367.4916040090425</v>
+        <v>1210.393037299881</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>215540.4465025496</v>
@@ -4536,6 +4539,9 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>475505.0514294247</v>
+      </c>
+      <c r="X26" t="n">
+        <v>367.4916040090425</v>
       </c>
     </row>
   </sheetData>
@@ -4549,7 +4555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4687,6 +4693,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -4736,19 +4752,22 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4821,6 +4840,12 @@
       <c r="V3" s="2" t="n">
         <v>0.3223803903634925</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -4891,6 +4916,12 @@
       <c r="V4" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -4908,10 +4939,10 @@
         <v>10</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.881896884283592</v>
+        <v>6.223128848904347</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4.881896884283592</v>
+        <v>6.223128848904347</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>5.102040816326531</v>
@@ -4960,6 +4991,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>5.124599030923125</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4.881896884283592</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.881896884283592</v>
       </c>
     </row>
     <row r="6">
@@ -4978,10 +5015,10 @@
         <v>38.37072454922788</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>12.32322407924027</v>
+        <v>18.10130675474342</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>15.94929274210823</v>
+        <v>25.20558388046248</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>22.27429047420717</v>
@@ -5030,6 +5067,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>22.32385000367074</v>
+      </c>
+      <c r="W6" t="n">
+        <v>12.32322407924027</v>
+      </c>
+      <c r="X6" t="n">
+        <v>15.94929274210823</v>
       </c>
     </row>
     <row r="7">
@@ -5048,10 +5091,10 @@
         <v>169.1845454758088</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34.23132986499605</v>
+        <v>58.79467325663467</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>53.05644145839639</v>
+        <v>103.84897625005</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>117.6812039542221</v>
@@ -5100,6 +5143,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>135.3221220669738</v>
+      </c>
+      <c r="W7" t="n">
+        <v>34.23132986499605</v>
+      </c>
+      <c r="X7" t="n">
+        <v>53.05644145839639</v>
       </c>
     </row>
     <row r="8">
@@ -5118,10 +5167,10 @@
         <v>10.04715034159078</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4.897735417991635</v>
+        <v>6.246415572627058</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4.817279090322625</v>
+        <v>6.157451550719678</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>8.469311156097827</v>
@@ -5170,6 +5219,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>3.463436398110999</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.897735417991635</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.817279090322625</v>
       </c>
     </row>
     <row r="9">
@@ -5188,10 +5243,10 @@
         <v>19.94737422009919</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>7.853920505552195</v>
+        <v>10.76764438018142</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>13.27020707414865</v>
+        <v>22.43097915721846</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>123.8880416542777</v>
@@ -5240,6 +5295,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>287.8073165313254</v>
+      </c>
+      <c r="W9" t="n">
+        <v>7.853920505552195</v>
+      </c>
+      <c r="X9" t="n">
+        <v>13.27020707414865</v>
       </c>
     </row>
     <row r="10">
@@ -5258,10 +5319,10 @@
         <v>34.85398325632856</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11.53393332626138</v>
+        <v>16.77111671055687</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>23.95459789823945</v>
+        <v>46.13615066233237</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>122.1105836808597</v>
@@ -5310,6 +5371,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>263.2496245661334</v>
+      </c>
+      <c r="W10" t="n">
+        <v>11.53393332626138</v>
+      </c>
+      <c r="X10" t="n">
+        <v>23.95459789823945</v>
       </c>
     </row>
     <row r="11">
@@ -5328,10 +5395,10 @@
         <v>102.7246442466901</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>24.27818587440447</v>
+        <v>39.56283070651072</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>49.2544955448092</v>
+        <v>98.6116966075774</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>47.33250285039934</v>
@@ -5380,6 +5447,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>51.83930781587688</v>
+      </c>
+      <c r="W11" t="n">
+        <v>24.27818587440447</v>
+      </c>
+      <c r="X11" t="n">
+        <v>49.2544955448092</v>
       </c>
     </row>
     <row r="12">
@@ -5398,10 +5471,10 @@
         <v>75.37386174427014</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>19.61701044712016</v>
+        <v>30.94067580555833</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>40.48007979745215</v>
+        <v>88.6615481068378</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>77.81175772311749</v>
@@ -5450,6 +5523,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>130.2728115138363</v>
+      </c>
+      <c r="W12" t="n">
+        <v>19.61701044712016</v>
+      </c>
+      <c r="X12" t="n">
+        <v>40.48007979745215</v>
       </c>
     </row>
     <row r="13">
@@ -5468,10 +5547,10 @@
         <v>306.2377129713688</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>51.50764169239473</v>
+        <v>94.17864685117233</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>86.24822714450288</v>
+        <v>186.9483287457134</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>292.9935734046114</v>
@@ -5520,6 +5599,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>333.7708523617817</v>
+      </c>
+      <c r="W13" t="n">
+        <v>51.50764169239473</v>
+      </c>
+      <c r="X13" t="n">
+        <v>86.24822714450288</v>
       </c>
     </row>
     <row r="14">
@@ -5538,10 +5623,10 @@
         <v>88.56163218810677</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>21.9205342021058</v>
+        <v>35.16658028962565</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>63.18533145172209</v>
+        <v>139.9688809708051</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>125.5029051695527</v>
@@ -5590,6 +5675,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>138.4479745464489</v>
+      </c>
+      <c r="W14" t="n">
+        <v>21.9205342021058</v>
+      </c>
+      <c r="X14" t="n">
+        <v>63.18533145172209</v>
       </c>
     </row>
     <row r="15">
@@ -5608,10 +5699,10 @@
         <v>10</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>4.881896884283592</v>
+        <v>6.223128848904347</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>4.881896884283592</v>
+        <v>6.223128848904347</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>10.19754055468341</v>
@@ -5660,6 +5751,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>9.496174338698417</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4.881896884283592</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4.881896884283592</v>
       </c>
     </row>
     <row r="16">
@@ -5678,10 +5775,10 @@
         <v>735.9198461865436</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>94.20345180303136</v>
+        <v>188.9246547467871</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>274.1184846161911</v>
+        <v>772.3589140731528</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>1003.748472342274</v>
@@ -5730,6 +5827,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>1512.932250311565</v>
+      </c>
+      <c r="W16" t="n">
+        <v>94.20345180303136</v>
+      </c>
+      <c r="X16" t="n">
+        <v>274.1184846161911</v>
       </c>
     </row>
     <row r="17">
@@ -5748,10 +5851,10 @@
         <v>47.87525527224734</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>14.35176635029988</v>
+        <v>21.57858629762915</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>47.93631306284109</v>
+        <v>107.4629161326766</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>123.6827696735525</v>
@@ -5800,6 +5903,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>174.3038165894203</v>
+      </c>
+      <c r="W17" t="n">
+        <v>14.35176635029988</v>
+      </c>
+      <c r="X17" t="n">
+        <v>47.93631306284109</v>
       </c>
     </row>
     <row r="18">
@@ -5818,10 +5927,10 @@
         <v>153.5063191216989</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>32.01412407426785</v>
+        <v>54.42563084569721</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>100.6878204145854</v>
+        <v>236.6828022651465</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>159.0613711885023</v>
@@ -5870,6 +5979,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>211.8709226329803</v>
+      </c>
+      <c r="W18" t="n">
+        <v>32.01412407426783</v>
+      </c>
+      <c r="X18" t="n">
+        <v>100.6878204145854</v>
       </c>
     </row>
     <row r="19">
@@ -5888,10 +6003,10 @@
         <v>1113.102078243138</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>125.2590957378396</v>
+        <v>262.4070949788439</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>249.9812478195048</v>
+        <v>672.1889581826362</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>421.7498448185209</v>
@@ -5940,6 +6055,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>1212.57805917571</v>
+      </c>
+      <c r="W19" t="n">
+        <v>125.2590957378396</v>
+      </c>
+      <c r="X19" t="n">
+        <v>249.9812478195048</v>
       </c>
     </row>
     <row r="20">
@@ -5958,10 +6079,10 @@
         <v>1254.298198323786</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>135.9951668482977</v>
+        <v>288.507746425553</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>530.8757765188035</v>
+        <v>1782.49431863192</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>1013.570171471442</v>
@@ -6010,6 +6131,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>2057.246558511828</v>
+      </c>
+      <c r="W20" t="n">
+        <v>135.9951668482977</v>
+      </c>
+      <c r="X20" t="n">
+        <v>530.8757765188035</v>
       </c>
     </row>
     <row r="21">
@@ -6028,10 +6155,10 @@
         <v>1254.312676029027</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>135.996247738189</v>
+        <v>288.5103905458261</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>384.9639588136019</v>
+        <v>1152.508392338651</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1331.752693342869</v>
@@ -6080,6 +6207,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>3182.729383356123</v>
+      </c>
+      <c r="W21" t="n">
+        <v>135.996247738189</v>
+      </c>
+      <c r="X21" t="n">
+        <v>384.9639588136019</v>
       </c>
     </row>
     <row r="22">
@@ -6098,10 +6231,10 @@
         <v>1377.951482341825</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>145.0910757257476</v>
+        <v>310.8703778357537</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>354.0160885041838</v>
+        <v>1019.11674600522</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>804.6273553053973</v>
@@ -6150,6 +6283,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>1005.016369881499</v>
+      </c>
+      <c r="W22" t="n">
+        <v>145.0910757257474</v>
+      </c>
+      <c r="X22" t="n">
+        <v>354.0160885041838</v>
       </c>
     </row>
     <row r="23">
@@ -6168,10 +6307,10 @@
         <v>1182.417917160679</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>130.5795261988503</v>
+        <v>275.3006232985392</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>655.0984682910046</v>
+        <v>2443.4114085821</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>848.8851915781844</v>
@@ -6220,6 +6359,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>2161.079708508654</v>
+      </c>
+      <c r="W23" t="n">
+        <v>130.5795261988503</v>
+      </c>
+      <c r="X23" t="n">
+        <v>655.0984682910046</v>
       </c>
     </row>
     <row r="24">
@@ -6238,10 +6383,10 @@
         <v>378.0255773200133</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>59.54587886365636</v>
+        <v>111.320330100519</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>236.0536915685313</v>
+        <v>691.0777210943435</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>2128.450324204537</v>
@@ -6290,6 +6435,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>3360.569290714359</v>
+      </c>
+      <c r="W24" t="n">
+        <v>59.54587886365636</v>
+      </c>
+      <c r="X24" t="n">
+        <v>236.0536915685313</v>
       </c>
     </row>
     <row r="25">
@@ -6308,10 +6459,10 @@
         <v>2569.289220312157</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>222.8221513847066</v>
+        <v>509.8254375061286</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1308.685036527036</v>
+        <v>5573.824861515769</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>1955.186859493807</v>
@@ -6361,6 +6512,12 @@
       <c r="V25" s="2" t="n">
         <v>4280.685882503204</v>
       </c>
+      <c r="W25" t="n">
+        <v>222.8221513847066</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1308.685036527036</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -6378,10 +6535,10 @@
         <v>1106.631322071805</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>124.757235171582</v>
+        <v>261.195153950476</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>418.7723011987895</v>
+        <v>1335.321685246217</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>255333.6498407797</v>
@@ -6430,6 +6587,12 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>533729.0919429567</v>
+      </c>
+      <c r="W26" t="n">
+        <v>124.757235171582</v>
+      </c>
+      <c r="X26" t="n">
+        <v>418.7723011987895</v>
       </c>
     </row>
   </sheetData>
@@ -6443,7 +6606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6581,6 +6744,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -6630,19 +6803,22 @@
       <c r="O2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6715,6 +6891,12 @@
       <c r="V3" s="2" t="n">
         <v>0.3223803903634925</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -6785,6 +6967,12 @@
       <c r="V4" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -6802,10 +6990,10 @@
         <v>10</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.881896884283592</v>
+        <v>6.223128848904347</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4.881896884283592</v>
+        <v>6.223128848904347</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>5.102040816326531</v>
@@ -6854,6 +7042,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>5.124599030923125</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4.881896884283592</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.881896884283592</v>
       </c>
     </row>
     <row r="6">
@@ -6872,10 +7066,10 @@
         <v>38.37072454922788</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>12.32322407924027</v>
+        <v>18.10130675474342</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>15.94929274210823</v>
+        <v>25.20558388046248</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>22.27429047420717</v>
@@ -6924,6 +7118,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>22.32385000367074</v>
+      </c>
+      <c r="W6" t="n">
+        <v>12.32322407924027</v>
+      </c>
+      <c r="X6" t="n">
+        <v>15.94929274210823</v>
       </c>
     </row>
     <row r="7">
@@ -6942,10 +7142,10 @@
         <v>169.1845454758088</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34.23132986499605</v>
+        <v>58.79467325663467</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>53.05644145839639</v>
+        <v>103.84897625005</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>117.6812039542221</v>
@@ -6994,6 +7194,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>135.3221220669738</v>
+      </c>
+      <c r="W7" t="n">
+        <v>34.23132986499605</v>
+      </c>
+      <c r="X7" t="n">
+        <v>53.05644145839639</v>
       </c>
     </row>
     <row r="8">
@@ -7012,10 +7218,10 @@
         <v>10.04715034159078</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4.897735417991635</v>
+        <v>6.246415572627058</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4.817279090322625</v>
+        <v>6.157451550719678</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>8.469311156097827</v>
@@ -7064,6 +7270,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>3.463436398110999</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.897735417991635</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.817279090322625</v>
       </c>
     </row>
     <row r="9">
@@ -7082,10 +7294,10 @@
         <v>19.94737422009919</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>7.853920505552195</v>
+        <v>10.76764438018142</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>13.27020707414865</v>
+        <v>22.43097915721846</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>123.8880416542777</v>
@@ -7134,6 +7346,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>287.8073165313254</v>
+      </c>
+      <c r="W9" t="n">
+        <v>7.853920505552195</v>
+      </c>
+      <c r="X9" t="n">
+        <v>13.27020707414865</v>
       </c>
     </row>
     <row r="10">
@@ -7152,10 +7370,10 @@
         <v>34.85398325632856</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11.53393332626138</v>
+        <v>16.77111671055687</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>23.95459789823945</v>
+        <v>46.13615066233237</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>122.1105836808597</v>
@@ -7204,6 +7422,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>263.2496245661334</v>
+      </c>
+      <c r="W10" t="n">
+        <v>11.53393332626138</v>
+      </c>
+      <c r="X10" t="n">
+        <v>23.95459789823945</v>
       </c>
     </row>
     <row r="11">
@@ -7222,10 +7446,10 @@
         <v>102.7246442466901</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>24.27818587440447</v>
+        <v>39.56283070651072</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>49.2544955448092</v>
+        <v>98.6116966075774</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>47.33250285039934</v>
@@ -7274,6 +7498,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>51.83930781587688</v>
+      </c>
+      <c r="W11" t="n">
+        <v>24.27818587440447</v>
+      </c>
+      <c r="X11" t="n">
+        <v>49.2544955448092</v>
       </c>
     </row>
     <row r="12">
@@ -7292,10 +7522,10 @@
         <v>75.37386174427014</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>19.61701044712016</v>
+        <v>30.94067580555833</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>40.48007979745215</v>
+        <v>88.6615481068378</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>77.81175772311749</v>
@@ -7344,6 +7574,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>130.2728115138363</v>
+      </c>
+      <c r="W12" t="n">
+        <v>19.61701044712016</v>
+      </c>
+      <c r="X12" t="n">
+        <v>40.48007979745215</v>
       </c>
     </row>
     <row r="13">
@@ -7362,10 +7598,10 @@
         <v>306.2377129713688</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>51.50764169239473</v>
+        <v>94.17864685117233</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>86.24822714450288</v>
+        <v>186.9483287457134</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>292.9935734046114</v>
@@ -7414,6 +7650,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>333.7708523617817</v>
+      </c>
+      <c r="W13" t="n">
+        <v>51.50764169239473</v>
+      </c>
+      <c r="X13" t="n">
+        <v>86.24822714450288</v>
       </c>
     </row>
     <row r="14">
@@ -7432,10 +7674,10 @@
         <v>88.56163218810677</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>21.9205342021058</v>
+        <v>35.16658028962565</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>63.18533145172209</v>
+        <v>139.9688809708051</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>125.5029051695527</v>
@@ -7484,6 +7726,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>138.4479745464489</v>
+      </c>
+      <c r="W14" t="n">
+        <v>21.9205342021058</v>
+      </c>
+      <c r="X14" t="n">
+        <v>63.18533145172209</v>
       </c>
     </row>
     <row r="15">
@@ -7502,10 +7750,10 @@
         <v>10</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>4.881896884283592</v>
+        <v>6.223128848904347</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>4.881896884283592</v>
+        <v>6.223128848904347</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>10.19754055468341</v>
@@ -7554,6 +7802,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>9.496174338698417</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4.881896884283592</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4.881896884283592</v>
       </c>
     </row>
     <row r="16">
@@ -7572,10 +7826,10 @@
         <v>735.9198461865436</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>94.20345180303136</v>
+        <v>188.9246547467871</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>274.1184846161911</v>
+        <v>772.3589140731528</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>1003.748472342274</v>
@@ -7624,6 +7878,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>1512.932250311565</v>
+      </c>
+      <c r="W16" t="n">
+        <v>94.20345180303136</v>
+      </c>
+      <c r="X16" t="n">
+        <v>274.1184846161911</v>
       </c>
     </row>
     <row r="17">
@@ -7642,10 +7902,10 @@
         <v>47.87525527224734</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>14.35176635029988</v>
+        <v>21.57858629762915</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>47.93631306284109</v>
+        <v>107.4629161326766</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>123.6827696735525</v>
@@ -7694,6 +7954,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>174.3038165894203</v>
+      </c>
+      <c r="W17" t="n">
+        <v>14.35176635029988</v>
+      </c>
+      <c r="X17" t="n">
+        <v>47.93631306284109</v>
       </c>
     </row>
     <row r="18">
@@ -7712,10 +7978,10 @@
         <v>153.5063191216989</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>32.01412407426785</v>
+        <v>54.42563084569721</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>100.6878204145854</v>
+        <v>236.6828022651465</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>159.0613711885023</v>
@@ -7764,6 +8030,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>211.8709226329803</v>
+      </c>
+      <c r="W18" t="n">
+        <v>32.01412407426783</v>
+      </c>
+      <c r="X18" t="n">
+        <v>100.6878204145854</v>
       </c>
     </row>
     <row r="19">
@@ -7782,10 +8054,10 @@
         <v>1113.102078243138</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>125.2590957378396</v>
+        <v>262.4070949788439</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>249.9812478195048</v>
+        <v>672.1889581826362</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>421.7498448185209</v>
@@ -7834,6 +8106,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>1212.57805917571</v>
+      </c>
+      <c r="W19" t="n">
+        <v>125.2590957378396</v>
+      </c>
+      <c r="X19" t="n">
+        <v>249.9812478195048</v>
       </c>
     </row>
     <row r="20">
@@ -7852,10 +8130,10 @@
         <v>1254.298198323786</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>135.9951668482977</v>
+        <v>288.507746425553</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>530.8757765188035</v>
+        <v>1782.49431863192</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>1013.570171471442</v>
@@ -7904,6 +8182,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>2057.246558511828</v>
+      </c>
+      <c r="W20" t="n">
+        <v>135.9951668482977</v>
+      </c>
+      <c r="X20" t="n">
+        <v>530.8757765188035</v>
       </c>
     </row>
     <row r="21">
@@ -7922,10 +8206,10 @@
         <v>1254.312676029027</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>135.996247738189</v>
+        <v>288.5103905458261</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>384.9639588136019</v>
+        <v>1152.508392338651</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1331.752693342869</v>
@@ -7974,6 +8258,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>3182.729383356123</v>
+      </c>
+      <c r="W21" t="n">
+        <v>135.996247738189</v>
+      </c>
+      <c r="X21" t="n">
+        <v>384.9639588136019</v>
       </c>
     </row>
     <row r="22">
@@ -7992,10 +8282,10 @@
         <v>1377.951482341825</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>145.0910757257476</v>
+        <v>310.8703778357537</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>354.0160885041838</v>
+        <v>1019.11674600522</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>804.6273553053973</v>
@@ -8044,6 +8334,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>1005.016369881499</v>
+      </c>
+      <c r="W22" t="n">
+        <v>145.0910757257474</v>
+      </c>
+      <c r="X22" t="n">
+        <v>354.0160885041838</v>
       </c>
     </row>
     <row r="23">
@@ -8062,10 +8358,10 @@
         <v>1182.417917160679</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>130.5795261988503</v>
+        <v>275.3006232985392</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>655.0984682910046</v>
+        <v>2443.4114085821</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>848.8851915781844</v>
@@ -8114,6 +8410,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>2161.079708508654</v>
+      </c>
+      <c r="W23" t="n">
+        <v>130.5795261988503</v>
+      </c>
+      <c r="X23" t="n">
+        <v>655.0984682910046</v>
       </c>
     </row>
     <row r="24">
@@ -8132,10 +8434,10 @@
         <v>378.0255773200133</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>59.54587886365636</v>
+        <v>111.320330100519</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>236.0536915685313</v>
+        <v>691.0777210943435</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>2128.450324204537</v>
@@ -8184,6 +8486,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>3360.569290714359</v>
+      </c>
+      <c r="W24" t="n">
+        <v>59.54587886365636</v>
+      </c>
+      <c r="X24" t="n">
+        <v>236.0536915685313</v>
       </c>
     </row>
     <row r="25">
@@ -8202,10 +8510,10 @@
         <v>2569.289220312157</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>222.8221513847066</v>
+        <v>509.8254375061286</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1308.685036527036</v>
+        <v>5573.824861515769</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>1955.186859493807</v>
@@ -8255,6 +8563,12 @@
       <c r="V25" s="2" t="n">
         <v>4280.685882503204</v>
       </c>
+      <c r="W25" t="n">
+        <v>222.8221513847066</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1308.685036527036</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -8272,10 +8586,10 @@
         <v>1106.631322071805</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>124.757235171582</v>
+        <v>261.195153950476</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>418.7723011987895</v>
+        <v>1335.321685246217</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>255333.6498407797</v>
@@ -8324,6 +8638,12 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>533729.0919429567</v>
+      </c>
+      <c r="W26" t="n">
+        <v>124.757235171582</v>
+      </c>
+      <c r="X26" t="n">
+        <v>418.7723011987895</v>
       </c>
     </row>
   </sheetData>
@@ -8795,7 +9115,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
       <c r="AD2" s="2" t="n">
         <v>0.5160159405139225</v>
       </c>
@@ -8921,7 +9240,6 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Arabian_Sea_off_Karnataka (2000)</t>
@@ -8985,7 +9303,6 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" s="2" t="n">
         <v>0</v>
       </c>
@@ -9179,7 +9496,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
         <v>0.535114568397998</v>
       </c>
@@ -9281,7 +9597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9342,14 +9658,12 @@
       <c r="C2" s="2" t="n">
         <v>698.6957964207286</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0.170621684107626</v>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -9363,14 +9677,12 @@
       <c r="C3" s="2" t="n">
         <v>2189.941127281998</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.534784158066422</v>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -9379,19 +9691,17 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>291.4556411587741</v>
+        <v>568.4879724997598</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>291.4556411587741</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>568.4879724997598</v>
+      </c>
       <c r="E4" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.07117353874451138</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>0.1388249017093431</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -9400,22 +9710,22 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>893.3240333517341</v>
+        <v>2654.250271352967</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>893.3240333517341</v>
+        <v>2654.250271352967</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>803.1575703666068</v>
+        <v>2446.609691466923</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>4095</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.2181499470944405</v>
+        <v>0.6481685644329589</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1961312748148002</v>
+        <v>0.5974626841189067</v>
       </c>
     </row>
     <row r="6">
@@ -9816,6 +10126,50 @@
       </c>
       <c r="G21" s="2" t="n">
         <v>0.865753075262735</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>291.455641158774</v>
+      </c>
+      <c r="C22" t="n">
+        <v>291.455641158774</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4095</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.07117353874451136</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>893.3240333517341</v>
+      </c>
+      <c r="C23" t="n">
+        <v>893.3240333517341</v>
+      </c>
+      <c r="D23" t="n">
+        <v>803.1575703666068</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4095</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.2181499470944405</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.1961312748148002</v>
       </c>
     </row>
   </sheetData>
@@ -9951,7 +10305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9987,7 +10341,6 @@
           <t>NaN means not available, never zero. A basal source a method does not resolve is NaN, and a method that raised leaves its entire block NaN.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -10000,7 +10353,6 @@
           <t>sppr_all, sppr_inner and sppr_PP are the same table under three source scopes, mirroring get_PPR: sppr_all sums every basal source, sppr_inner drops Import, and sppr_PP drops Import and Detritus. Each is a flat groups x methods table -- rows are group seq with the group name in the first column, one column per method, no MultiIndex. Sums are taken over each method's own basal-source columns before aggregation; the per-source breakdown itself is not written to the workbook.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -10013,7 +10365,6 @@
           <t>SPPR_1986 and SPPR_1995 return one un-attributed SPPR column, so their value cannot be split into a PP-only part: they are NaN in sppr_PP (and in ppr_pp_only) while sppr_inner and sppr_all carry the total. A method that resolves no Detritus source (SPPR_2015) has sppr_inner equal to sppr_PP by construction.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -10026,7 +10377,6 @@
           <t>SPPR_2015() has no only_pp_det parameter (only_pp belongs to get_PPR / get_PPR2NPP_ratio). It is called bare here and PP-only filtering is applied downstream at the get_PPR layer, which is what the ppr_pp_only column and SUM_PP already do.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -10039,7 +10389,6 @@
           <t>Under det_open_mode='none' det_theta does not affect the recycling gain b at all (verified: identical b at theta = 1, 3 and 10). Do not read the health sheet as a theta sensitivity.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -10052,7 +10401,6 @@
           <t>MC runs use exclude_diverged=True, so draws graded FAIL on divergence are dropped as well as draws with a negative SPPR. The two are often the same draws rather than additive -- see the mc_diagnostics sheet for the split by cause.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -10065,7 +10413,6 @@
           <t>SPPR_EwE and the Monte-Carlo methods are called with silent=True rather than silent=False: PPRCalculator imports tqdm.notebook, whose bar needs ipywidgets and raises ImportError('IProgress not found') outside Jupyter, which makes those methods fail outright in a terminal run. Nothing is lost -- this exporter has its own progress bar, and the MC rejection counts appear in mc_diagnostics and in the run report.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -10078,7 +10425,6 @@
           <t>diagnose_sppr grades a CONFIGURATION, not a model: a model can be healthy under one TE_option and divergent under another. Read each row with its config_ columns.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -10091,7 +10437,6 @@
           <t>Every SPPR method, and every diagnose_sppr row, runs in a worker process with a wall-clock budget (180 s by default; --timeout SECONDS on the command line, method_timeout= from Python, and None or 0 to disable it). A method still running when the budget expires is killed and left NaN, exactly like a method that raised -- the status column of this sheet and the run report are the only places that say which of the two happened. A timeout is a statement about this machine and this model, not about the method: rerun it with a larger budget before reading anything into it.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -10135,7 +10480,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer consumption weights.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -10152,7 +10497,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nullspace form of the EwE path sum, global TE at the true mean (Jensen-able on TL).</t>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer consumption-weighted arithmetic mean (Jensen-able on TL).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10428,6 +10773,40 @@
         </is>
       </c>
       <c r="C30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>method: SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer catch weights. Consumer biomass fallback when consumer catch is zero.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>method: Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer catch-weighted arithmetic mean. Consumer biomass fallback when consumer catch is zero (Jensen-able on TL).</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
